--- a/engagement_survey_forms/002_organizational_fairness_perception_survey--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/002_organizational_fairness_perception_survey--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fair_diversity</t>
+          <t>fair_diversity_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fair Diversities</t>
+          <t>Fair Diversity 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fair_safety</t>
+          <t>fair_safety_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fair Safety</t>
+          <t>Fair Safety 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fair_sustainability</t>
+          <t>fair_sustainability_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fair Sustainibility</t>
+          <t>Fair Sustainability 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fair Sustainibility</t>
+          <t>Fair Sustainibility (3)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fair_equity_choices</t>
+          <t>fair_opportunities_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fair_opportunities_choices</t>
+          <t>fair_recognition_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fair_recognition_choices</t>
+          <t>fair_inclusion_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fair_inclusion_choices</t>
+          <t>fair_communication_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1454,29 +1454,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fair_communication_choices</t>
+          <t>fair_safety_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1505,488 +1505,318 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fair_safety_choices</t>
+          <t>fair_health_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fair_safety_choices</t>
+          <t>fair_health_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fair_safety_choices</t>
+          <t>fair_health_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fair_health_choices</t>
+          <t>fair_environment_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fair_health_choices</t>
+          <t>fair_environment_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fair_health_choices</t>
+          <t>fair_environment_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fair_health_choices</t>
+          <t>fair_diversity_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>fair_health_choices</t>
+          <t>fair_diversity_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>fair_health_choices</t>
+          <t>fair_equity_diversity_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option_6</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Option 6</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fair_environment_choices</t>
+          <t>fair_equity_diversity_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>fair_environment_choices</t>
+          <t>fair_equity_inclusion_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>fair_environment_choices</t>
+          <t>fair_equity_inclusion_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>fair_environment_choices</t>
+          <t>fair_equity_inclusion_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>fair_environment_choices</t>
+          <t>fair_diversity_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>fair_diversity_choices</t>
+          <t>fair_diversity_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>fair_diversity_choices</t>
+          <t>fair_sustainability_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>fair_equity_diversity_choices</t>
+          <t>fair_sustainability_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fair_equity_diversity_choices</t>
+          <t>fair_sustainability_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>fair_equity_inclusion_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>fair_equity_inclusion_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>fair_equity_inclusion_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>fair_equity_inclusion_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>fair_diversity_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fair_diversity_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fair_sustainability_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>fair_sustainability_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>fair_sustainability_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>fair_sustainability_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Option 4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
